--- a/Maurice+ Contribution par rubrique.xlsx
+++ b/Maurice+ Contribution par rubrique.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\EXPAT\MAURICE APP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16EF416F-EF27-42E2-8B01-B6352D010925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE3DC8A5-AA08-4269-A8F9-2850F834DBBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="75" activeTab="82" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="12" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="1" r:id="rId1"/>
@@ -108,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8432" uniqueCount="6508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8455" uniqueCount="6521">
   <si>
     <t>Maurice+ — Contribution par rubrique</t>
   </si>
@@ -19643,6 +19643,45 @@
   </si>
   <si>
     <t>Que faire quand pleut</t>
+  </si>
+  <si>
+    <t>vérifier qu'il est dans la rubrique équitation (à supprimer d'ici)</t>
+  </si>
+  <si>
+    <t>vérifier qu'il est dans la rubrique golf (à supprimer d'ici)</t>
+  </si>
+  <si>
+    <t>à supprimer</t>
+  </si>
+  <si>
+    <t>à mettre dans plongée</t>
+  </si>
+  <si>
+    <t>Kayak, snorkeling, parachute ascentionnel</t>
+  </si>
+  <si>
+    <t>multisports</t>
+  </si>
+  <si>
+    <t>plongée</t>
+  </si>
+  <si>
+    <t>Mettre la tranche de prix des abonnements et les différentes activités possibles</t>
+  </si>
+  <si>
+    <t>à mettre dans Business et TTV</t>
+  </si>
+  <si>
+    <t>AD Events</t>
+  </si>
+  <si>
+    <t>Club de vacances, centre aéré, périscolaire Ecole du Nord</t>
+  </si>
+  <si>
+    <t>http://www.adeventsports.com/</t>
+  </si>
+  <si>
+    <t>à mettre dans viewpoint</t>
   </si>
 </sst>
 </file>
@@ -19768,8 +19807,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
@@ -19777,6 +19814,8 @@
     <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -20086,7 +20125,7 @@
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="4" max="4" width="43.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.25">
@@ -21423,13 +21462,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>629</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -21668,13 +21707,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>653</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -22572,13 +22611,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>846</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -22660,13 +22699,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>847</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -22858,13 +22897,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>868</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -22957,7 +22996,9 @@
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
-      <c r="E9" s="7"/>
+      <c r="E9" s="11" t="s">
+        <v>6510</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
@@ -22979,7 +23020,9 @@
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
-      <c r="E11" s="7"/>
+      <c r="E11" s="11" t="s">
+        <v>6520</v>
+      </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
@@ -23020,7 +23063,9 @@
         <v>899</v>
       </c>
       <c r="D14" s="4"/>
-      <c r="E14" s="7"/>
+      <c r="E14" s="11" t="s">
+        <v>6510</v>
+      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
@@ -23072,7 +23117,9 @@
       <c r="D18" s="4" t="s">
         <v>911</v>
       </c>
-      <c r="E18" s="7"/>
+      <c r="E18" s="11" t="s">
+        <v>6510</v>
+      </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
@@ -23087,7 +23134,9 @@
       <c r="D19" s="4" t="s">
         <v>896</v>
       </c>
-      <c r="E19" s="7"/>
+      <c r="E19" s="11" t="s">
+        <v>6510</v>
+      </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
@@ -23100,7 +23149,9 @@
       <c r="D20" s="4" t="s">
         <v>917</v>
       </c>
-      <c r="E20" s="7"/>
+      <c r="E20" s="11" t="s">
+        <v>6510</v>
+      </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
@@ -23165,13 +23216,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>918</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -23580,13 +23631,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>985</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -25540,13 +25591,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>1423</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -25916,7 +25967,9 @@
       <c r="D28" s="4" t="s">
         <v>1507</v>
       </c>
-      <c r="E28" s="7"/>
+      <c r="E28" s="7" t="s">
+        <v>6510</v>
+      </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
@@ -25944,7 +25997,9 @@
         <v>1514</v>
       </c>
       <c r="D30" s="4"/>
-      <c r="E30" s="7"/>
+      <c r="E30" s="7" t="s">
+        <v>6510</v>
+      </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
@@ -26362,13 +26417,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>1601</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -26456,7 +26511,9 @@
       <c r="D8" s="4" t="s">
         <v>1618</v>
       </c>
-      <c r="E8" s="7"/>
+      <c r="E8" s="7" t="s">
+        <v>6516</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
@@ -26471,14 +26528,26 @@
       <c r="D9" s="4" t="s">
         <v>1621</v>
       </c>
-      <c r="E9" s="7"/>
+      <c r="E9" s="7" t="s">
+        <v>6516</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="7"/>
+      <c r="A10" s="4" t="s">
+        <v>6517</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C10" s="4">
+        <v>23057890476</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>6519</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>6518</v>
+      </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
@@ -26536,13 +26605,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>1622</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -28497,13 +28566,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -28699,13 +28768,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>2046</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -28871,13 +28940,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>2064</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -28974,13 +29043,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>2069</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -29077,13 +29146,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>2072</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -30761,13 +30830,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>2435</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -31915,13 +31984,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>2673</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -35216,7 +35285,7 @@
       <c r="E244" s="7"/>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A245" s="10" t="s">
+      <c r="A245" s="8" t="s">
         <v>3339</v>
       </c>
       <c r="B245" s="4" t="s">
@@ -38514,13 +38583,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>4004</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -39251,13 +39320,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>4128</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -39581,13 +39650,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>219</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -39856,13 +39925,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>4176</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -40565,13 +40634,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>4306</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -41948,13 +42017,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>4620</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -42292,13 +42361,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>4681</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -42951,13 +43020,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>4801</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -43661,13 +43730,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>4935</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -43984,13 +44053,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>4993</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -44343,13 +44412,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>5051</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -44377,7 +44446,7 @@
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="14" t="s">
         <v>6503</v>
       </c>
     </row>
@@ -44390,7 +44459,7 @@
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="14" t="s">
         <v>6501</v>
       </c>
     </row>
@@ -44403,7 +44472,7 @@
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="14" t="s">
         <v>6506</v>
       </c>
     </row>
@@ -44416,7 +44485,7 @@
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="14" t="s">
         <v>6500</v>
       </c>
     </row>
@@ -44431,18 +44500,18 @@
         <v>5059</v>
       </c>
       <c r="D8" s="4"/>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="14" t="s">
         <v>6502</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="9" t="s">
         <v>6504</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="14" t="s">
         <v>6505</v>
       </c>
     </row>
@@ -44451,21 +44520,21 @@
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
-      <c r="E10" s="16"/>
+      <c r="E10" s="14"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
-      <c r="E11" s="16"/>
+      <c r="E11" s="14"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
-      <c r="E12" s="16"/>
+      <c r="E12" s="14"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
@@ -44502,13 +44571,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>5060</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -45369,13 +45438,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>5238</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -46043,13 +46112,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -46340,13 +46409,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>5372</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -46472,13 +46541,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>5377</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -46573,13 +46642,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>5378</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -46807,13 +46876,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>5401</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -47685,13 +47754,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>5402</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -48397,13 +48466,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>5403</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -48660,13 +48729,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>5404</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -49070,13 +49139,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>5405</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -49487,13 +49556,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>5406</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -49804,13 +49873,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>5407</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -49899,21 +49968,21 @@
   <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="1" max="1" width="55" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="51.85546875" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="4" max="4" width="70.42578125" customWidth="1"/>
     <col min="5" max="5" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>312</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -50016,7 +50085,9 @@
       <c r="D9" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="E9" s="7"/>
+      <c r="E9" s="7" t="s">
+        <v>6508</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
@@ -50162,7 +50233,9 @@
       <c r="D19" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="E19" s="7"/>
+      <c r="E19" s="7" t="s">
+        <v>6509</v>
+      </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
@@ -50220,7 +50293,9 @@
         <v>386</v>
       </c>
       <c r="D23" s="4"/>
-      <c r="E23" s="7"/>
+      <c r="E23" s="7" t="s">
+        <v>6512</v>
+      </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
@@ -50235,7 +50310,9 @@
       <c r="D24" s="4" t="s">
         <v>390</v>
       </c>
-      <c r="E24" s="7"/>
+      <c r="E24" s="7" t="s">
+        <v>6511</v>
+      </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
@@ -50336,7 +50413,9 @@
       <c r="D31" s="4" t="s">
         <v>416</v>
       </c>
-      <c r="E31" s="7"/>
+      <c r="E31" s="7" t="s">
+        <v>6510</v>
+      </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
@@ -50362,7 +50441,9 @@
         <v>422</v>
       </c>
       <c r="D33" s="4"/>
-      <c r="E33" s="7"/>
+      <c r="E33" s="7" t="s">
+        <v>6514</v>
+      </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
@@ -50581,7 +50662,9 @@
       <c r="D48" s="4" t="s">
         <v>477</v>
       </c>
-      <c r="E48" s="7"/>
+      <c r="E48" s="7" t="s">
+        <v>6510</v>
+      </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
@@ -50592,7 +50675,9 @@
       </c>
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
-      <c r="E49" s="7"/>
+      <c r="E49" s="7" t="s">
+        <v>6513</v>
+      </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
@@ -50687,13 +50772,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>5408</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -50803,13 +50888,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>5409</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -51050,13 +51135,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>5410</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -51192,13 +51277,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>5411</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -51399,13 +51484,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>5412</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -51661,13 +51746,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>5413</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -52179,13 +52264,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>5518</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -52494,13 +52579,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>5569</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -53234,13 +53319,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>5727</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -53535,13 +53620,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>5778</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -53733,13 +53818,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>488</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -54009,13 +54094,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>5797</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -54214,13 +54299,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>5824</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -54457,13 +54542,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>5863</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -54573,13 +54658,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>5871</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -54702,13 +54787,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>5882</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -54842,13 +54927,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>5895</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -55094,13 +55179,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>5934</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -55849,13 +55934,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>6086</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -56186,13 +56271,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>6144</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -56274,13 +56359,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>6145</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -56362,13 +56447,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>534</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -56400,27 +56485,27 @@
       <c r="D4" s="4" t="s">
         <v>538</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="11" t="s">
         <v>6499</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="9" t="s">
         <v>6483</v>
       </c>
       <c r="B5" s="4"/>
-      <c r="C5" s="12">
+      <c r="C5" s="10">
         <v>23058579977</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>6484</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="11" t="s">
         <v>6486</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="9" t="s">
         <v>6485</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -56430,29 +56515,29 @@
       <c r="D6" s="4" t="s">
         <v>6487</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="11" t="s">
         <v>6486</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="9" t="s">
         <v>6489</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>6498</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="13" t="s">
         <v>6497</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>6495</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="11" t="s">
         <v>6496</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="9" t="s">
         <v>6490</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -56460,18 +56545,18 @@
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="11" t="s">
         <v>6494</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="9" t="s">
         <v>6491</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="9" t="s">
         <v>6492</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="12">
         <v>23057723999</v>
       </c>
       <c r="D9" s="4"/>
@@ -56509,13 +56594,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>6146</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -56675,13 +56760,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>6159</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -56791,13 +56876,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>6162</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -57267,13 +57352,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>6252</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -57520,13 +57605,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>6297</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -57754,13 +57839,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>6333</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -57924,13 +58009,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>6353</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -58227,13 +58312,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>6405</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -58427,13 +58512,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>6433</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -58515,13 +58600,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>6434</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -58603,13 +58688,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>539</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -58749,7 +58834,9 @@
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
-      <c r="E12" s="7"/>
+      <c r="E12" s="7" t="s">
+        <v>6515</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
@@ -58807,13 +58894,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>6435</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -58895,13 +58982,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>6436</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -58983,13 +59070,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>6437</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -59071,13 +59158,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>6438</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -59159,13 +59246,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>6439</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -59361,13 +59448,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>6469</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -59515,13 +59602,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>6478</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -59603,13 +59690,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>6479</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -59691,13 +59778,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>6480</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -59779,13 +59866,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>6481</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -59867,13 +59954,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>554</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">

--- a/Maurice+ Contribution par rubrique.xlsx
+++ b/Maurice+ Contribution par rubrique.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\EXPAT\MAURICE APP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE3DC8A5-AA08-4269-A8F9-2850F834DBBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93625179-E6FC-4D6F-97A7-8261B88C438B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="12" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="1" r:id="rId1"/>
@@ -103,12 +103,25 @@
     <sheet name="EVT_Culturels" sheetId="86" r:id="rId88"/>
     <sheet name="EVT_Business" sheetId="87" r:id="rId89"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8455" uniqueCount="6521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8458" uniqueCount="6524">
   <si>
     <t>Maurice+ — Contribution par rubrique</t>
   </si>
@@ -19682,6 +19695,15 @@
   </si>
   <si>
     <t>à mettre dans viewpoint</t>
+  </si>
+  <si>
+    <t>Demande en cours pour en rajouter (centre?!!)</t>
+  </si>
+  <si>
+    <t>Qu'est ce que le crayon et nom associé sur les fiches?</t>
+  </si>
+  <si>
+    <t>à compléter avec photo et court descriptif des randos</t>
   </si>
 </sst>
 </file>
@@ -19765,7 +19787,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -19782,6 +19804,12 @@
         <fgColor rgb="FFFFF9DB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -19796,7 +19824,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -19816,6 +19844,7 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -46108,7 +46137,7 @@
     <col min="2" max="2" width="40" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="50" customWidth="1"/>
+    <col min="5" max="5" width="53.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
@@ -46119,6 +46148,11 @@
       <c r="C1" s="16"/>
       <c r="D1" s="16"/>
       <c r="E1" s="16"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E2" t="s">
+        <v>6521</v>
+      </c>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -53825,6 +53859,11 @@
       <c r="C1" s="16"/>
       <c r="D1" s="16"/>
       <c r="E1" s="16"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E2" t="s">
+        <v>6522</v>
+      </c>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -58834,7 +58873,7 @@
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="17" t="s">
         <v>6515</v>
       </c>
     </row>
@@ -59962,6 +60001,11 @@
       <c r="D1" s="16"/>
       <c r="E1" s="16"/>
     </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E2" t="s">
+        <v>6523</v>
+      </c>
+    </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>185</v>

--- a/Maurice+ Contribution par rubrique.xlsx
+++ b/Maurice+ Contribution par rubrique.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\EXPAT\MAURICE APP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{060BE661-8AA4-4AC0-8B2D-1E551F4BF441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF30AAD9-4164-4C56-981C-A8993C63404E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="13" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="1" r:id="rId1"/>
@@ -118,12 +118,16 @@
     <sheet name="EVT_Culturels" sheetId="103" r:id="rId103"/>
     <sheet name="EVT_Business" sheetId="104" r:id="rId104"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'ACT_Complexes sportifs'!$A$3:$E$179</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'ACT_Randonnée &amp; trail'!$A$3:$E$3</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10018" uniqueCount="7473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10135" uniqueCount="7491">
   <si>
     <t>Maurice+ — Contribution par rubrique</t>
   </si>
@@ -22542,13 +22546,94 @@
   </si>
   <si>
     <t>Safari de 2h en 4*4. Note: vérifier qu ecelui ci est bien aussi dans réserves naturelels</t>
+  </si>
+  <si>
+    <t>à supprimer (doublon avec Vallée Adventaure)</t>
+  </si>
+  <si>
+    <t>à mettre dans activités enfants et famille</t>
+  </si>
+  <si>
+    <t>à mettre dans randonnée-trail</t>
+  </si>
+  <si>
+    <t>à supprimer doublon avec LSC</t>
+  </si>
+  <si>
+    <t>à déplacer dans shooping - magasins sport</t>
+  </si>
+  <si>
+    <t>à déplacer dans padel-tennis</t>
+  </si>
+  <si>
+    <t>à déplacer dans gym/fitness</t>
+  </si>
+  <si>
+    <t>à déplacer dans gym-fitness</t>
+  </si>
+  <si>
+    <t>compléter: 4,8km 500mD+. Attention aux moustqiues. Faire une synthèse plus courte de: Cet itinéraire est une entreprise aventureuse qui commence par une randonnée difficile à travers les champs de canne à sucre avant d'escalader l'épine dorsale de la montagne. Attendez-vous à un défi physique ; le sentier est accidenté, escarpé et souvent envahi par la végétation, ce qui vous obligera à utiliser vos mains pour escalader les parois rocheuses volcaniques et à vous frayer un chemin dans les sentiers parsemés de racines.
+La section de la "Tête de Lion" offre une véritable exposition, où l'on doit être très précis. Votre effort vous vaudra l'un des plus beaux panoramas de l'île Maurice : une vue à 360 degrés sur le lagon turquoise, la ceinture sucrière et le site de la bataille de Grand Port en 1810, la seule victoire navale des Français napoléoniens. En raison de la technicité de l'ascension et du risque élevé de glissade sur le sol argileux, ce sentier ne doit être emprunté que par temps sec et par des randonneurs expérimentés.</t>
+  </si>
+  <si>
+    <t>Sentier d'Alexandra Falls</t>
+  </si>
+  <si>
+    <t>2,7km 157mD+ 1h30.  Synthèse courte à faire : Partez découvrir cet itinéraire aller-retour de 2,7-km près de St. Martin, Savanne. Généralement considéré comme un parcours modéré, il faut en moyenne 1 h 2 min pour le parcourir. C’est un endroit très prisé pour l'ornithologie, la randonnée et le VTT, vous croiserez donc probablement du monde pendant votre excursion. La meilleure période de visite est de mars à janvier. Les chiens sont les bienvenus et peuvent être lâchés à certains endroits.</t>
+  </si>
+  <si>
+    <t>Parc national gorges rivière noire</t>
+  </si>
+  <si>
+    <t>6,9 km
+Distance
+456 m
+Dénivelé positif
+SYNTHESE BEAUCOUP PLUS COURTE A FAIRE:
+S'élevant de façon spectaculaire dans le lagon turquoise de l'océan Indien, ce monolithe basaltique emblématique offre l'une des aventures les plus importantes sur le plan culturel et les plus exigeantes sur le plan physique à l'île Maurice. Classé au patrimoine mondial de l'UNESCO, le Morne Brabant est imprégné de l'histoire tragique de la "République marron". Il a servi de refuge aux esclaves en fuite qui, selon la légende, ont préféré se jeter du haut des falaises plutôt que d'être repris.
+Le sentier se divise en deux parties. La première partie est une piste large et trompeuse qui serpente doucement à travers une forêt sèche, accessible à la plupart des personnes en bonne condition physique. Cependant, après le panneau d'avertissement sur le plateau, l'itinéraire se transforme en un véritable défi d'alpinisme. Les randonneurs doivent s'attaquer à une escalade technique, en se servant de leurs mains et de leurs pieds pour franchir des parois rocheuses abruptes et la fameuse brèche en "V". L'exposition est réelle et le basalte peut être glissant, il est donc essentiel d'être sûr de soi.
+Votre récompense à la croix du sommet (490 mètres) est un panorama sans pareil sur les récifs du sud-ouest et l'illusion de la fameuse "cascade sous-marine" au large de la côte. Bien que la randonnée indépendante soit autorisée, un guide est fortement recommandé pour l'ascension finale en raison de la nature technique de l'ascension. Commencez au lever du soleil pour éviter la chaleur tropicale et la foule sur les crêtes étroites.</t>
+  </si>
+  <si>
+    <t>2,3 km
+Distance
+116 m
+Dénivelé positif
+Boucle
+SYNTHSE BEACOUP PLUS COURTE DE: Voici une magnifique randonnée qui longe la rivière Tamarin et mène aux chutes de Tamarin (également connues sous le nom de chutes de Tamarind), une série de sept cascades sur le plateau central de l'île Maurice. Le sentier traverse une épaisse forêt verdoyante et offre des vues époustouflantes. À la bonne saison, il est possible de se baigner dans ce qui ressemble à un paradis. Les randonneurs recommandent d'apporter une serviette légère, de la crème solaire, un maillot de bain et de bonnes chaussures avec une bonne adhérence ou même des chaussures d'eau. Veuillez noter que le chemin près des chutes d'eau peut être très glissant. Certains passages peuvent nécessiter l'utilisation des mains pour garder l'équilibre et ce sentier ne doit pas être emprunté après la pluie.</t>
+  </si>
+  <si>
+    <t>Boucle courte des 7 cascades</t>
+  </si>
+  <si>
+    <t>4,3 km
+Distance
+370 m
+Dénivelé positif
+Aller-retour
+Ce sentier gratifiant vous emmène au sommet de la troisième plus haute montagne de l'île Maurice, Le Pouce (812 m), connu localement sous le nom de "The Thumb" (le pouce) en raison de son pinacle rocheux caractéristique. Il vous conduit à travers des champs de canne à sucre et des forêts tropicales luxuriantes avant d'atteindre les hauteurs rocheuses balayées par le vent.
+L'itinéraire le plus populaire et le plus accessible part du village de Petit Verger (près de Saint-Pierre) et suit un sentier clairement balisé qui traverse des champs de canne à sucre et des forêts avant de déboucher sur des pentes herbeuses. À l'approche du sommet, le terrain se transforme en une escalade raide et physique qui nécessite des chaussures solides et l'utilisation des mains pour naviguer sur la roche volcanique.
+Vous serez récompensé par une vue à 360 degrés sur la capitale Port Louis, la chaîne de Moka et les îles du nord comme Coin de Mire. Les randonneurs doivent être prêts à affronter la boue glissante, surtout après les fréquentes pluies de l'île, qui peuvent rendre le sentier dangereux.</t>
+  </si>
+  <si>
+    <t>5,8 km
+Distance
+327 m
+Dénivelé positif
+Boucle
+Embarquez pour une aventure palpitante le long de la rivière Tamarind, qui abrite les emblématiques 7 Cascades (Tamarind Falls). Cet itinéraire près d'Henrietta est moins une randonnée qu'une escalade dans le canyon ; le "sentier" est souvent une piste faible et boueuse qui vous oblige à vous accrocher aux racines des goyaviers et à naviguer sur des parois abruptes de basalte pour atteindre les bassins cachés.
+Vous descendrez profondément dans la gorge, en sautant sur les rochers de la rivière et en passant derrière des rideaux d'eau tonitruants. Le terrain est célèbre pour être glissant et escarpé, ce qui exige des chaussures à haute adhérence et souvent l'utilisation des mains (ou de cordes fixes) pour franchir les dénivelés en toute sécurité.
+Bien que la baignade dans les bassins frais et émeraude soit rafraîchissante, les visiteurs doivent être vigilants face aux crues soudaines et au réseau confus de sentiers informels. En raison de la nature technique de la descente et du manque de signalisation, il est fortement recommandé de faire appel à un guide local pour découvrir en toute sécurité la séquence complète de ces magnifiques chutes, dont la principale fait une chute de près de 300 mètres.</t>
+  </si>
+  <si>
+    <t>Boucle des cascades</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -22584,6 +22669,29 @@
       <sz val="10"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="24"/>
+      <color rgb="FF161F13"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF535B52"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF161F13"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -22610,7 +22718,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -22619,6 +22727,25 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -26414,7 +26541,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -26450,7 +26577,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>1185</v>
       </c>
@@ -26459,7 +26586,9 @@
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
+      <c r="E4" s="8" t="s">
+        <v>7485</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
@@ -26487,7 +26616,7 @@
       </c>
       <c r="E6" s="5"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="328.5" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>1193</v>
       </c>
@@ -26496,7 +26625,9 @@
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
+      <c r="E7" s="8" t="s">
+        <v>7481</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
@@ -26509,7 +26640,7 @@
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>1197</v>
       </c>
@@ -26518,7 +26649,9 @@
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
+      <c r="E9" s="13" t="s">
+        <v>7488</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
@@ -26872,7 +27005,44 @@
       <c r="D37" s="5"/>
       <c r="E37" s="5"/>
     </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="5" t="s">
+        <v>7482</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>7484</v>
+      </c>
+      <c r="E38" t="s">
+        <v>7483</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="315" x14ac:dyDescent="0.25">
+      <c r="A39" s="5" t="s">
+        <v>7487</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>7486</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A40" s="14" t="s">
+        <v>7490</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>7489</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E41" s="10"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E42" s="11"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E43" s="12"/>
+    </row>
   </sheetData>
+  <autoFilter ref="A3:E3" xr:uid="{00000000-0001-0000-1200-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
@@ -26882,6 +27052,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr>
+    <tabColor theme="6" tint="0.59999389629810485"/>
+  </sheetPr>
   <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -31358,13 +31531,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr>
+    <tabColor theme="6" tint="0.59999389629810485"/>
+  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="4" max="4" width="28" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="50" customWidth="1"/>
   </cols>
   <sheetData>
@@ -31448,7 +31624,9 @@
       <c r="D7" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="E7" s="5"/>
+      <c r="E7" s="5" t="s">
+        <v>7473</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
@@ -31491,7 +31669,9 @@
       <c r="D10" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="E10" s="5"/>
+      <c r="E10" s="5" t="s">
+        <v>7474</v>
+      </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
@@ -31506,7 +31686,9 @@
       <c r="D11" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="E11" s="5"/>
+      <c r="E11" s="5" t="s">
+        <v>7475</v>
+      </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
@@ -31536,7 +31718,9 @@
       <c r="D13" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="E13" s="5"/>
+      <c r="E13" s="5" t="s">
+        <v>7474</v>
+      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
@@ -31551,7 +31735,9 @@
       <c r="D14" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="E14" s="5"/>
+      <c r="E14" s="5" t="s">
+        <v>7474</v>
+      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
@@ -31564,7 +31750,9 @@
         <v>291</v>
       </c>
       <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
+      <c r="E15" s="5" t="s">
+        <v>7475</v>
+      </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
@@ -31579,7 +31767,9 @@
       <c r="D16" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="E16" s="5"/>
+      <c r="E16" s="5" t="s">
+        <v>7473</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -35369,13 +35559,16 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr filterMode="1">
+    <tabColor theme="6" tint="0.59999389629810485"/>
+  </sheetPr>
   <dimension ref="A1:E179"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="4" max="4" width="28" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="50" customWidth="1"/>
   </cols>
   <sheetData>
@@ -35405,7 +35598,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>294</v>
       </c>
@@ -35480,7 +35673,7 @@
       </c>
       <c r="E8" s="5"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>314</v>
       </c>
@@ -35493,7 +35686,9 @@
       <c r="D9" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="E9" s="5"/>
+      <c r="E9" s="5" t="s">
+        <v>7478</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
@@ -35508,9 +35703,11 @@
       <c r="D10" s="5" t="s">
         <v>321</v>
       </c>
-      <c r="E10" s="5"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E10" s="5" t="s">
+        <v>7480</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>322</v>
       </c>
@@ -35523,9 +35720,11 @@
       <c r="D11" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="E11" s="5"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E11" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>326</v>
       </c>
@@ -35538,9 +35737,11 @@
       <c r="D12" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="E12" s="5"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E12" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>330</v>
       </c>
@@ -35555,7 +35756,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>334</v>
       </c>
@@ -35568,7 +35769,9 @@
       <c r="D14" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="E14" s="5"/>
+      <c r="E14" s="5" t="s">
+        <v>7479</v>
+      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
@@ -35683,7 +35886,7 @@
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>362</v>
       </c>
@@ -35696,7 +35899,9 @@
       <c r="D24" s="5" t="s">
         <v>365</v>
       </c>
-      <c r="E24" s="5"/>
+      <c r="E24" s="5" t="s">
+        <v>7478</v>
+      </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
@@ -35711,7 +35916,7 @@
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>369</v>
       </c>
@@ -35722,9 +35927,11 @@
         <v>371</v>
       </c>
       <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E26" s="5" t="s">
+        <v>7476</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>372</v>
       </c>
@@ -35733,7 +35940,9 @@
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
+      <c r="E27" s="5" t="s">
+        <v>7479</v>
+      </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
@@ -35748,7 +35957,7 @@
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>377</v>
       </c>
@@ -35759,9 +35968,11 @@
         <v>379</v>
       </c>
       <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E29" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>380</v>
       </c>
@@ -35774,9 +35985,11 @@
       <c r="D30" s="5" t="s">
         <v>383</v>
       </c>
-      <c r="E30" s="5"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E30" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>384</v>
       </c>
@@ -35789,9 +36002,11 @@
       <c r="D31" s="5" t="s">
         <v>387</v>
       </c>
-      <c r="E31" s="5"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E31" s="5" t="s">
+        <v>7477</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>388</v>
       </c>
@@ -35804,9 +36019,11 @@
       <c r="D32" s="5" t="s">
         <v>390</v>
       </c>
-      <c r="E32" s="5"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E32" s="5" t="s">
+        <v>7478</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>391</v>
       </c>
@@ -35819,9 +36036,11 @@
       <c r="D33" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="E33" s="5"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E33" s="5" t="s">
+        <v>7478</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>392</v>
       </c>
@@ -35832,9 +36051,11 @@
         <v>394</v>
       </c>
       <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E34" s="5" t="s">
+        <v>7478</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>395</v>
       </c>
@@ -35845,7 +36066,9 @@
         <v>397</v>
       </c>
       <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
+      <c r="E35" s="5" t="s">
+        <v>7478</v>
+      </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
@@ -35858,7 +36081,7 @@
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>400</v>
       </c>
@@ -35869,9 +36092,11 @@
         <v>402</v>
       </c>
       <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E37" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
         <v>403</v>
       </c>
@@ -35884,9 +36109,11 @@
       <c r="D38" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="E38" s="5"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E38" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>407</v>
       </c>
@@ -35899,7 +36126,9 @@
       <c r="D39" s="5" t="s">
         <v>410</v>
       </c>
-      <c r="E39" s="5"/>
+      <c r="E39" s="5" t="s">
+        <v>7479</v>
+      </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
@@ -35914,7 +36143,7 @@
       <c r="D40" s="5"/>
       <c r="E40" s="5"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>414</v>
       </c>
@@ -35927,9 +36156,11 @@
       <c r="D41" s="5" t="s">
         <v>417</v>
       </c>
-      <c r="E41" s="5"/>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E41" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>418</v>
       </c>
@@ -35942,9 +36173,11 @@
       <c r="D42" s="5" t="s">
         <v>421</v>
       </c>
-      <c r="E42" s="5"/>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E42" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>422</v>
       </c>
@@ -35957,9 +36190,11 @@
       <c r="D43" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="E43" s="5"/>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E43" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>426</v>
       </c>
@@ -35970,9 +36205,11 @@
         <v>428</v>
       </c>
       <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E44" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
         <v>429</v>
       </c>
@@ -35983,7 +36220,9 @@
         <v>431</v>
       </c>
       <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
+      <c r="E45" s="5" t="s">
+        <v>7479</v>
+      </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
@@ -36000,7 +36239,7 @@
       </c>
       <c r="E46" s="5"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
         <v>436</v>
       </c>
@@ -36011,9 +36250,11 @@
         <v>438</v>
       </c>
       <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E47" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
         <v>439</v>
       </c>
@@ -36024,9 +36265,11 @@
         <v>441</v>
       </c>
       <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E48" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
         <v>442</v>
       </c>
@@ -36037,9 +36280,11 @@
         <v>444</v>
       </c>
       <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E49" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
         <v>445</v>
       </c>
@@ -36050,9 +36295,11 @@
         <v>447</v>
       </c>
       <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E50" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
         <v>448</v>
       </c>
@@ -36065,9 +36312,11 @@
       <c r="D51" s="5" t="s">
         <v>451</v>
       </c>
-      <c r="E51" s="5"/>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E51" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
         <v>452</v>
       </c>
@@ -36078,9 +36327,11 @@
         <v>454</v>
       </c>
       <c r="D52" s="5"/>
-      <c r="E52" s="5"/>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E52" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
         <v>455</v>
       </c>
@@ -36093,9 +36344,11 @@
       <c r="D53" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="E53" s="5"/>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E53" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
         <v>458</v>
       </c>
@@ -36106,7 +36359,9 @@
         <v>460</v>
       </c>
       <c r="D54" s="5"/>
-      <c r="E54" s="5"/>
+      <c r="E54" s="5" t="s">
+        <v>7479</v>
+      </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
@@ -36138,7 +36393,7 @@
       </c>
       <c r="E56" s="5"/>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
         <v>468</v>
       </c>
@@ -36149,7 +36404,9 @@
         <v>470</v>
       </c>
       <c r="D57" s="5"/>
-      <c r="E57" s="5"/>
+      <c r="E57" s="5" t="s">
+        <v>7479</v>
+      </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
@@ -36166,7 +36423,7 @@
       </c>
       <c r="E58" s="5"/>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
         <v>475</v>
       </c>
@@ -36177,9 +36434,11 @@
         <v>477</v>
       </c>
       <c r="D59" s="5"/>
-      <c r="E59" s="5"/>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E59" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
         <v>478</v>
       </c>
@@ -36192,9 +36451,11 @@
       <c r="D60" s="5" t="s">
         <v>481</v>
       </c>
-      <c r="E60" s="5"/>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E60" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
         <v>482</v>
       </c>
@@ -36205,9 +36466,11 @@
         <v>484</v>
       </c>
       <c r="D61" s="5"/>
-      <c r="E61" s="5"/>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E61" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
         <v>485</v>
       </c>
@@ -36218,9 +36481,11 @@
         <v>487</v>
       </c>
       <c r="D62" s="5"/>
-      <c r="E62" s="5"/>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E62" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
         <v>488</v>
       </c>
@@ -36231,9 +36496,11 @@
         <v>490</v>
       </c>
       <c r="D63" s="5"/>
-      <c r="E63" s="5"/>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E63" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
         <v>491</v>
       </c>
@@ -36244,7 +36511,9 @@
         <v>493</v>
       </c>
       <c r="D64" s="5"/>
-      <c r="E64" s="5"/>
+      <c r="E64" s="5" t="s">
+        <v>7479</v>
+      </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
@@ -36259,7 +36528,7 @@
       <c r="D65" s="5"/>
       <c r="E65" s="5"/>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
         <v>497</v>
       </c>
@@ -36270,9 +36539,11 @@
         <v>499</v>
       </c>
       <c r="D66" s="5"/>
-      <c r="E66" s="5"/>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E66" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
         <v>500</v>
       </c>
@@ -36283,9 +36554,11 @@
         <v>502</v>
       </c>
       <c r="D67" s="5"/>
-      <c r="E67" s="5"/>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E67" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
         <v>503</v>
       </c>
@@ -36294,7 +36567,9 @@
       </c>
       <c r="C68" s="5"/>
       <c r="D68" s="5"/>
-      <c r="E68" s="5"/>
+      <c r="E68" s="5" t="s">
+        <v>7479</v>
+      </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
@@ -36309,7 +36584,7 @@
       <c r="D69" s="5"/>
       <c r="E69" s="5"/>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
         <v>508</v>
       </c>
@@ -36320,7 +36595,9 @@
         <v>493</v>
       </c>
       <c r="D70" s="5"/>
-      <c r="E70" s="5"/>
+      <c r="E70" s="5" t="s">
+        <v>7479</v>
+      </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
@@ -36337,7 +36614,7 @@
       </c>
       <c r="E71" s="5"/>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
         <v>514</v>
       </c>
@@ -36350,9 +36627,11 @@
       <c r="D72" s="5" t="s">
         <v>517</v>
       </c>
-      <c r="E72" s="5"/>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E72" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
         <v>518</v>
       </c>
@@ -36363,9 +36642,11 @@
         <v>520</v>
       </c>
       <c r="D73" s="5"/>
-      <c r="E73" s="5"/>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E73" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
         <v>521</v>
       </c>
@@ -36376,9 +36657,11 @@
       <c r="D74" s="5" t="s">
         <v>523</v>
       </c>
-      <c r="E74" s="5"/>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E74" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
         <v>524</v>
       </c>
@@ -36389,9 +36672,11 @@
         <v>526</v>
       </c>
       <c r="D75" s="5"/>
-      <c r="E75" s="5"/>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E75" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
         <v>527</v>
       </c>
@@ -36400,7 +36685,9 @@
       </c>
       <c r="C76" s="5"/>
       <c r="D76" s="5"/>
-      <c r="E76" s="5"/>
+      <c r="E76" s="5" t="s">
+        <v>7479</v>
+      </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
@@ -36437,7 +36724,7 @@
       <c r="D79" s="5"/>
       <c r="E79" s="5"/>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
         <v>536</v>
       </c>
@@ -36446,9 +36733,11 @@
       </c>
       <c r="C80" s="5"/>
       <c r="D80" s="5"/>
-      <c r="E80" s="5"/>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E80" s="5" t="s">
+        <v>7478</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
         <v>538</v>
       </c>
@@ -36459,9 +36748,11 @@
         <v>540</v>
       </c>
       <c r="D81" s="5"/>
-      <c r="E81" s="5"/>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E81" s="5" t="s">
+        <v>7478</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
         <v>541</v>
       </c>
@@ -36474,9 +36765,11 @@
       <c r="D82" s="5" t="s">
         <v>544</v>
       </c>
-      <c r="E82" s="5"/>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E82" s="5" t="s">
+        <v>7478</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
         <v>545</v>
       </c>
@@ -36485,9 +36778,11 @@
       </c>
       <c r="C83" s="5"/>
       <c r="D83" s="5"/>
-      <c r="E83" s="5"/>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E83" s="5" t="s">
+        <v>7478</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
         <v>547</v>
       </c>
@@ -36498,9 +36793,11 @@
         <v>549</v>
       </c>
       <c r="D84" s="5"/>
-      <c r="E84" s="5"/>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E84" s="5" t="s">
+        <v>7478</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
         <v>550</v>
       </c>
@@ -36511,7 +36808,9 @@
         <v>552</v>
       </c>
       <c r="D85" s="5"/>
-      <c r="E85" s="5"/>
+      <c r="E85" s="5" t="s">
+        <v>7478</v>
+      </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
@@ -36580,7 +36879,7 @@
       <c r="D90" s="5"/>
       <c r="E90" s="5"/>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
         <v>568</v>
       </c>
@@ -36593,9 +36892,11 @@
       <c r="D91" s="5" t="s">
         <v>571</v>
       </c>
-      <c r="E91" s="5"/>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E91" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
         <v>572</v>
       </c>
@@ -36604,9 +36905,11 @@
       </c>
       <c r="C92" s="5"/>
       <c r="D92" s="5"/>
-      <c r="E92" s="5"/>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E92" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
         <v>574</v>
       </c>
@@ -36617,9 +36920,11 @@
         <v>576</v>
       </c>
       <c r="D93" s="5"/>
-      <c r="E93" s="5"/>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E93" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
         <v>577</v>
       </c>
@@ -36628,9 +36933,11 @@
       </c>
       <c r="C94" s="5"/>
       <c r="D94" s="5"/>
-      <c r="E94" s="5"/>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E94" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
         <v>579</v>
       </c>
@@ -36641,9 +36948,11 @@
         <v>581</v>
       </c>
       <c r="D95" s="5"/>
-      <c r="E95" s="5"/>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E95" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
         <v>582</v>
       </c>
@@ -36654,9 +36963,11 @@
         <v>584</v>
       </c>
       <c r="D96" s="5"/>
-      <c r="E96" s="5"/>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E96" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
         <v>585</v>
       </c>
@@ -36667,9 +36978,11 @@
       <c r="D97" s="5" t="s">
         <v>587</v>
       </c>
-      <c r="E97" s="5"/>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E97" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
         <v>588</v>
       </c>
@@ -36682,9 +36995,11 @@
       <c r="D98" s="5" t="s">
         <v>591</v>
       </c>
-      <c r="E98" s="5"/>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E98" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
         <v>592</v>
       </c>
@@ -36697,9 +37012,11 @@
       <c r="D99" s="5" t="s">
         <v>595</v>
       </c>
-      <c r="E99" s="5"/>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E99" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
         <v>596</v>
       </c>
@@ -36712,9 +37029,11 @@
       <c r="D100" s="5" t="s">
         <v>599</v>
       </c>
-      <c r="E100" s="5"/>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E100" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
         <v>600</v>
       </c>
@@ -36725,9 +37044,11 @@
         <v>602</v>
       </c>
       <c r="D101" s="5"/>
-      <c r="E101" s="5"/>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E101" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
         <v>603</v>
       </c>
@@ -36738,9 +37059,11 @@
         <v>605</v>
       </c>
       <c r="D102" s="5"/>
-      <c r="E102" s="5"/>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E102" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
         <v>606</v>
       </c>
@@ -36753,9 +37076,11 @@
       <c r="D103" s="5" t="s">
         <v>609</v>
       </c>
-      <c r="E103" s="5"/>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E103" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
         <v>610</v>
       </c>
@@ -36766,9 +37091,11 @@
         <v>612</v>
       </c>
       <c r="D104" s="5"/>
-      <c r="E104" s="5"/>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E104" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
         <v>613</v>
       </c>
@@ -36777,7 +37104,9 @@
       </c>
       <c r="C105" s="5"/>
       <c r="D105" s="5"/>
-      <c r="E105" s="5"/>
+      <c r="E105" s="5" t="s">
+        <v>7479</v>
+      </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
@@ -36824,7 +37153,7 @@
       </c>
       <c r="E108" s="5"/>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
         <v>627</v>
       </c>
@@ -36835,7 +37164,9 @@
         <v>629</v>
       </c>
       <c r="D109" s="5"/>
-      <c r="E109" s="5"/>
+      <c r="E109" s="5" t="s">
+        <v>7479</v>
+      </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
@@ -36923,7 +37254,7 @@
       </c>
       <c r="E115" s="5"/>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="5" t="s">
         <v>651</v>
       </c>
@@ -36934,9 +37265,11 @@
         <v>653</v>
       </c>
       <c r="D116" s="5"/>
-      <c r="E116" s="5"/>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E116" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
         <v>654</v>
       </c>
@@ -36947,9 +37280,11 @@
         <v>656</v>
       </c>
       <c r="D117" s="5"/>
-      <c r="E117" s="5"/>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E117" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="s">
         <v>657</v>
       </c>
@@ -36962,9 +37297,11 @@
       <c r="D118" s="5" t="s">
         <v>660</v>
       </c>
-      <c r="E118" s="5"/>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E118" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
         <v>661</v>
       </c>
@@ -36975,9 +37312,11 @@
         <v>663</v>
       </c>
       <c r="D119" s="5"/>
-      <c r="E119" s="5"/>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E119" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="5" t="s">
         <v>664</v>
       </c>
@@ -36990,9 +37329,11 @@
       <c r="D120" s="5" t="s">
         <v>667</v>
       </c>
-      <c r="E120" s="5"/>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E120" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
         <v>668</v>
       </c>
@@ -37003,9 +37344,11 @@
         <v>670</v>
       </c>
       <c r="D121" s="5"/>
-      <c r="E121" s="5"/>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E121" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="5" t="s">
         <v>671</v>
       </c>
@@ -37014,9 +37357,11 @@
       </c>
       <c r="C122" s="5"/>
       <c r="D122" s="5"/>
-      <c r="E122" s="5"/>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E122" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
         <v>673</v>
       </c>
@@ -37027,9 +37372,11 @@
         <v>675</v>
       </c>
       <c r="D123" s="5"/>
-      <c r="E123" s="5"/>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E123" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="5" t="s">
         <v>676</v>
       </c>
@@ -37042,9 +37389,11 @@
       <c r="D124" s="5" t="s">
         <v>679</v>
       </c>
-      <c r="E124" s="5"/>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E124" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="s">
         <v>680</v>
       </c>
@@ -37055,9 +37404,11 @@
         <v>682</v>
       </c>
       <c r="D125" s="5"/>
-      <c r="E125" s="5"/>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E125" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="5" t="s">
         <v>683</v>
       </c>
@@ -37068,9 +37419,11 @@
         <v>685</v>
       </c>
       <c r="D126" s="5"/>
-      <c r="E126" s="5"/>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E126" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="5" t="s">
         <v>686</v>
       </c>
@@ -37081,7 +37434,9 @@
         <v>688</v>
       </c>
       <c r="D127" s="5"/>
-      <c r="E127" s="5"/>
+      <c r="E127" s="5" t="s">
+        <v>7479</v>
+      </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="5" t="s">
@@ -37098,7 +37453,7 @@
       </c>
       <c r="E128" s="5"/>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="5" t="s">
         <v>692</v>
       </c>
@@ -37109,7 +37464,9 @@
         <v>694</v>
       </c>
       <c r="D129" s="5"/>
-      <c r="E129" s="5"/>
+      <c r="E129" s="5" t="s">
+        <v>7479</v>
+      </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="5" t="s">
@@ -37124,7 +37481,7 @@
       <c r="D130" s="5"/>
       <c r="E130" s="5"/>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="5" t="s">
         <v>697</v>
       </c>
@@ -37133,7 +37490,9 @@
       </c>
       <c r="C131" s="5"/>
       <c r="D131" s="5"/>
-      <c r="E131" s="5"/>
+      <c r="E131" s="5" t="s">
+        <v>7478</v>
+      </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="5" t="s">
@@ -37200,7 +37559,7 @@
       </c>
       <c r="E136" s="5"/>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="5" t="s">
         <v>714</v>
       </c>
@@ -37211,9 +37570,11 @@
         <v>716</v>
       </c>
       <c r="D137" s="5"/>
-      <c r="E137" s="5"/>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E137" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="5" t="s">
         <v>717</v>
       </c>
@@ -37224,9 +37585,11 @@
         <v>719</v>
       </c>
       <c r="D138" s="5"/>
-      <c r="E138" s="5"/>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E138" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="5" t="s">
         <v>720</v>
       </c>
@@ -37237,7 +37600,9 @@
         <v>722</v>
       </c>
       <c r="D139" s="5"/>
-      <c r="E139" s="5"/>
+      <c r="E139" s="5" t="s">
+        <v>7479</v>
+      </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="5" t="s">
@@ -37254,7 +37619,7 @@
       </c>
       <c r="E140" s="5"/>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="5" t="s">
         <v>727</v>
       </c>
@@ -37265,7 +37630,9 @@
         <v>729</v>
       </c>
       <c r="D141" s="5"/>
-      <c r="E141" s="5"/>
+      <c r="E141" s="5" t="s">
+        <v>7479</v>
+      </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="5" t="s">
@@ -37289,7 +37656,7 @@
       <c r="D143" s="5"/>
       <c r="E143" s="5"/>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="5" t="s">
         <v>734</v>
       </c>
@@ -37300,7 +37667,9 @@
         <v>736</v>
       </c>
       <c r="D144" s="5"/>
-      <c r="E144" s="5"/>
+      <c r="E144" s="5" t="s">
+        <v>7479</v>
+      </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="5" t="s">
@@ -37315,7 +37684,7 @@
       <c r="D145" s="5"/>
       <c r="E145" s="5"/>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="5" t="s">
         <v>740</v>
       </c>
@@ -37326,7 +37695,9 @@
         <v>742</v>
       </c>
       <c r="D146" s="5"/>
-      <c r="E146" s="5"/>
+      <c r="E146" s="5" t="s">
+        <v>7479</v>
+      </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="5" t="s">
@@ -37339,7 +37710,7 @@
       <c r="D147" s="5"/>
       <c r="E147" s="5"/>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="5" t="s">
         <v>745</v>
       </c>
@@ -37350,7 +37721,9 @@
         <v>747</v>
       </c>
       <c r="D148" s="5"/>
-      <c r="E148" s="5"/>
+      <c r="E148" s="5" t="s">
+        <v>7479</v>
+      </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="5" t="s">
@@ -37365,7 +37738,7 @@
       <c r="D149" s="5"/>
       <c r="E149" s="5"/>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="5" t="s">
         <v>751</v>
       </c>
@@ -37376,7 +37749,9 @@
         <v>753</v>
       </c>
       <c r="D150" s="5"/>
-      <c r="E150" s="5"/>
+      <c r="E150" s="5" t="s">
+        <v>7479</v>
+      </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="5" t="s">
@@ -37391,7 +37766,7 @@
       <c r="D151" s="5"/>
       <c r="E151" s="5"/>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="5" t="s">
         <v>757</v>
       </c>
@@ -37402,7 +37777,9 @@
         <v>759</v>
       </c>
       <c r="D152" s="5"/>
-      <c r="E152" s="5"/>
+      <c r="E152" s="5" t="s">
+        <v>7479</v>
+      </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="5" t="s">
@@ -37430,7 +37807,7 @@
       <c r="D154" s="5"/>
       <c r="E154" s="5"/>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="5" t="s">
         <v>766</v>
       </c>
@@ -37441,7 +37818,9 @@
         <v>768</v>
       </c>
       <c r="D155" s="5"/>
-      <c r="E155" s="5"/>
+      <c r="E155" s="5" t="s">
+        <v>7479</v>
+      </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="5" t="s">
@@ -37458,7 +37837,7 @@
       </c>
       <c r="E156" s="5"/>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="5" t="s">
         <v>773</v>
       </c>
@@ -37467,9 +37846,11 @@
       </c>
       <c r="C157" s="5"/>
       <c r="D157" s="5"/>
-      <c r="E157" s="5"/>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E157" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="5" t="s">
         <v>775</v>
       </c>
@@ -37480,7 +37861,9 @@
         <v>777</v>
       </c>
       <c r="D158" s="5"/>
-      <c r="E158" s="5"/>
+      <c r="E158" s="5" t="s">
+        <v>7479</v>
+      </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="5" t="s">
@@ -37497,7 +37880,7 @@
       </c>
       <c r="E159" s="5"/>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="5" t="s">
         <v>782</v>
       </c>
@@ -37510,7 +37893,9 @@
       <c r="D160" s="5" t="s">
         <v>785</v>
       </c>
-      <c r="E160" s="5"/>
+      <c r="E160" s="5" t="s">
+        <v>7479</v>
+      </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="5" t="s">
@@ -37536,7 +37921,7 @@
       <c r="D162" s="5"/>
       <c r="E162" s="5"/>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="5" t="s">
         <v>791</v>
       </c>
@@ -37549,9 +37934,11 @@
       <c r="D163" s="5" t="s">
         <v>794</v>
       </c>
-      <c r="E163" s="5"/>
-    </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E163" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="5" t="s">
         <v>795</v>
       </c>
@@ -37562,9 +37949,11 @@
         <v>797</v>
       </c>
       <c r="D164" s="5"/>
-      <c r="E164" s="5"/>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E164" s="5" t="s">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="5" t="s">
         <v>798</v>
       </c>
@@ -37577,9 +37966,11 @@
       <c r="D165" s="5" t="s">
         <v>801</v>
       </c>
-      <c r="E165" s="5"/>
-    </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E165" s="5" t="s">
+        <v>7478</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="5" t="s">
         <v>802</v>
       </c>
@@ -37590,7 +37981,9 @@
         <v>804</v>
       </c>
       <c r="D166" s="5"/>
-      <c r="E166" s="5"/>
+      <c r="E166" s="5" t="s">
+        <v>7478</v>
+      </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" s="5" t="s">
@@ -37762,6 +38155,11 @@
       <c r="E179" s="5"/>
     </row>
   </sheetData>
+  <autoFilter ref="A3:E179" xr:uid="{00000000-0001-0000-0300-000000000000}">
+    <filterColumn colId="4">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
